--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/backend.devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3B1867-2A5E-2647-BB22-0ED7343DB694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F652C57A-02E9-E740-954D-E0289383F453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36380" yWindow="4980" windowWidth="18200" windowHeight="8500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="76">
   <si>
     <t>module</t>
   </si>
@@ -181,6 +181,78 @@
   </si>
   <si>
     <t>training-report</t>
+  </si>
+  <si>
+    <t>training-event</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>Kecamatan</t>
+  </si>
+  <si>
+    <t>training-subdistrict</t>
+  </si>
+  <si>
+    <t>app_registration</t>
+  </si>
+  <si>
+    <t>subdistrict</t>
+  </si>
+  <si>
+    <t>Desa</t>
+  </si>
+  <si>
+    <t>training-village</t>
+  </si>
+  <si>
+    <t>subdistrict/:subdistrict/village</t>
+  </si>
+  <si>
+    <t>Peserta</t>
+  </si>
+  <si>
+    <t>training-participant</t>
+  </si>
+  <si>
+    <t>event/:event/participant</t>
+  </si>
+  <si>
+    <t>Panitia</t>
+  </si>
+  <si>
+    <t>training-committee</t>
+  </si>
+  <si>
+    <t>event/:event/committee</t>
+  </si>
+  <si>
+    <t>Rundown</t>
+  </si>
+  <si>
+    <t>training-rundown</t>
+  </si>
+  <si>
+    <t>event/:event/rundown</t>
+  </si>
+  <si>
+    <t>Pretest</t>
+  </si>
+  <si>
+    <t>training-pretest</t>
+  </si>
+  <si>
+    <t>event/:event/pretest</t>
+  </si>
+  <si>
+    <t>Postest</t>
+  </si>
+  <si>
+    <t>training-postest</t>
+  </si>
+  <si>
+    <t>event/:event/postest</t>
   </si>
 </sst>
 </file>
@@ -651,7 +723,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -659,7 +731,7 @@
     <col min="4" max="4" width="23.5" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="6.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.1640625" style="6" bestFit="1" customWidth="1"/>
@@ -737,22 +809,22 @@
         <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="H3" s="5" t="b">
         <v>1</v>
@@ -761,6 +833,262 @@
         <v>0</v>
       </c>
       <c r="K3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>35</v>
       </c>
     </row>

--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/backend.devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F652C57A-02E9-E740-954D-E0289383F453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5CE8DE-01B0-D443-B9C8-9487815CE6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="71">
   <si>
     <t>module</t>
   </si>
@@ -39,42 +39,9 @@
     <t>permission</t>
   </si>
   <si>
-    <t>foundation</t>
-  </si>
-  <si>
-    <t>foundation-dashboard</t>
-  </si>
-  <si>
-    <t>superadmin, administrator</t>
-  </si>
-  <si>
     <t>*</t>
   </si>
   <si>
-    <t>foundation-position</t>
-  </si>
-  <si>
-    <t>foundation-communitymap</t>
-  </si>
-  <si>
-    <t>foundation-community</t>
-  </si>
-  <si>
-    <t>foundation-member</t>
-  </si>
-  <si>
-    <t>foundation-subdistrict</t>
-  </si>
-  <si>
-    <t>foundation-village</t>
-  </si>
-  <si>
-    <t>foundation-official</t>
-  </si>
-  <si>
-    <t>foundation-report</t>
-  </si>
-  <si>
     <t>superadmin</t>
   </si>
   <si>
@@ -253,6 +220,24 @@
   </si>
   <si>
     <t>event/:event/postest</t>
+  </si>
+  <si>
+    <t>training-presence</t>
+  </si>
+  <si>
+    <t>event/:event/presence</t>
+  </si>
+  <si>
+    <t>Absensi</t>
+  </si>
+  <si>
+    <t>member</t>
+  </si>
+  <si>
+    <t>chairman</t>
+  </si>
+  <si>
+    <t>superadmin, administrator, chairman, member</t>
   </si>
 </sst>
 </file>
@@ -645,60 +630,60 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="H2" s="5" t="b">
         <v>1</v>
@@ -710,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +708,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -742,57 +727,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H2" s="5" t="b">
         <v>1</v>
@@ -801,30 +786,30 @@
         <v>0</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H3" s="5" t="b">
         <v>1</v>
@@ -833,30 +818,30 @@
         <v>0</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H4" s="5" t="b">
         <v>0</v>
@@ -865,30 +850,30 @@
         <v>0</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H5" s="5" t="b">
         <v>0</v>
@@ -897,30 +882,30 @@
         <v>0</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="H6" s="5" t="b">
         <v>0</v>
@@ -929,30 +914,30 @@
         <v>0</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H7" s="5" t="b">
         <v>0</v>
@@ -961,30 +946,30 @@
         <v>0</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="H8" s="5" t="b">
         <v>0</v>
@@ -993,103 +978,135 @@
         <v>0</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="H9" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H10" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="5" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="H11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>35</v>
+      <c r="I12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1102,7 +1119,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -1118,106 +1135,128 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1230,7 +1269,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
@@ -1247,18 +1286,34 @@
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1271,12 +1326,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
@@ -1292,101 +1347,123 @@
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1399,12 +1476,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1424,128 +1501,156 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/backend.devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5CE8DE-01B0-D443-B9C8-9487815CE6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B00B7B-80B6-6546-9A3A-FEF03E8578AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="87">
   <si>
     <t>module</t>
   </si>
@@ -238,6 +238,54 @@
   </si>
   <si>
     <t>superadmin, administrator, chairman, member</t>
+  </si>
+  <si>
+    <t>Riwayat</t>
+  </si>
+  <si>
+    <t>training-history</t>
+  </si>
+  <si>
+    <t>history</t>
+  </si>
+  <si>
+    <t>history/:history/participant</t>
+  </si>
+  <si>
+    <t>history/:history/committee</t>
+  </si>
+  <si>
+    <t>history/:history/rundown</t>
+  </si>
+  <si>
+    <t>history/:history/pretest</t>
+  </si>
+  <si>
+    <t>history/:history/postest</t>
+  </si>
+  <si>
+    <t>history/:history/presence</t>
+  </si>
+  <si>
+    <t>training-history-participant</t>
+  </si>
+  <si>
+    <t>training-history-committee</t>
+  </si>
+  <si>
+    <t>training-history-rundown</t>
+  </si>
+  <si>
+    <t>training-history-pretest</t>
+  </si>
+  <si>
+    <t>training-history-postest</t>
+  </si>
+  <si>
+    <t>training-history-presence</t>
+  </si>
+  <si>
+    <t>view, show, search</t>
   </si>
 </sst>
 </file>
@@ -708,12 +756,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33.83203125" style="3" bestFit="1" customWidth="1"/>
@@ -1018,22 +1066,22 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H10" s="5" t="b">
         <v>1</v>
@@ -1050,22 +1098,22 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="H11" s="5" t="b">
         <v>0</v>
@@ -1082,30 +1130,254 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="5" t="b">
+      <c r="H17" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="s">
+      <c r="I17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="18" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1119,11 +1391,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62.83203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1231,7 +1503,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
@@ -1242,10 +1514,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1253,10 +1525,87 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1326,11 +1675,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1438,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>70</v>
@@ -1449,7 +1798,7 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -1460,9 +1809,86 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1476,11 +1902,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
@@ -1616,7 +2042,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>70</v>
@@ -1630,7 +2056,7 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -1644,12 +2070,110 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/backend.devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B00B7B-80B6-6546-9A3A-FEF03E8578AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEEE3C2-3858-9644-A9DA-D48B8B172897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -231,15 +231,6 @@
     <t>Absensi</t>
   </si>
   <si>
-    <t>member</t>
-  </si>
-  <si>
-    <t>chairman</t>
-  </si>
-  <si>
-    <t>superadmin, administrator, chairman, member</t>
-  </si>
-  <si>
     <t>Riwayat</t>
   </si>
   <si>
@@ -286,6 +277,15 @@
   </si>
   <si>
     <t>view, show, search</t>
+  </si>
+  <si>
+    <t>committee-chairman</t>
+  </si>
+  <si>
+    <t>committee-member</t>
+  </si>
+  <si>
+    <t>superadmin, administrator, committee-chairman, committee-member</t>
   </si>
 </sst>
 </file>
@@ -1066,13 +1066,13 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>42</v>
@@ -1081,7 +1081,7 @@
         <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H10" s="5" t="b">
         <v>1</v>
@@ -1104,7 +1104,7 @@
         <v>50</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>42</v>
@@ -1113,7 +1113,7 @@
         <v>38</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H11" s="5" t="b">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>53</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>42</v>
@@ -1145,7 +1145,7 @@
         <v>38</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H12" s="5" t="b">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>42</v>
@@ -1177,7 +1177,7 @@
         <v>38</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H13" s="5" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>42</v>
@@ -1209,7 +1209,7 @@
         <v>38</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H14" s="5" t="b">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>42</v>
@@ -1241,7 +1241,7 @@
         <v>38</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H15" s="5" t="b">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>42</v>
@@ -1273,7 +1273,7 @@
         <v>38</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H16" s="5" t="b">
         <v>0</v>
@@ -1503,7 +1503,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
@@ -1514,10 +1514,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1525,10 +1525,10 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1536,10 +1536,10 @@
         <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1547,10 +1547,10 @@
         <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1558,10 +1558,10 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1569,10 +1569,10 @@
         <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1654,7 +1654,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1662,7 +1662,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1680,7 +1680,7 @@
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.83203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
@@ -1702,7 +1702,7 @@
         <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1">
@@ -1713,7 +1713,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1">
@@ -1724,7 +1724,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
@@ -1735,7 +1735,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1">
@@ -1746,7 +1746,7 @@
         <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1">
@@ -1757,7 +1757,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1">
@@ -1768,7 +1768,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1">
@@ -1779,7 +1779,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1">
@@ -1787,10 +1787,10 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1798,10 +1798,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1809,10 +1809,10 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1820,10 +1820,10 @@
         <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1831,10 +1831,10 @@
         <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1842,10 +1842,10 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1853,10 +1853,10 @@
         <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1867,7 +1867,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1878,7 +1878,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1889,7 +1889,7 @@
         <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1907,7 +1907,7 @@
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.83203125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1933,7 +1933,7 @@
         <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
@@ -1947,7 +1947,7 @@
         <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
@@ -1961,7 +1961,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
@@ -1975,7 +1975,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -1989,7 +1989,7 @@
         <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
@@ -2003,7 +2003,7 @@
         <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -2017,7 +2017,7 @@
         <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
@@ -2031,7 +2031,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>4</v>
@@ -2042,10 +2042,10 @@
         <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>
@@ -2056,10 +2056,10 @@
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>4</v>
@@ -2070,10 +2070,10 @@
         <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
@@ -2084,10 +2084,10 @@
         <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
@@ -2098,10 +2098,10 @@
         <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -2112,10 +2112,10 @@
         <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -2126,10 +2126,10 @@
         <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
@@ -2143,7 +2143,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>4</v>
@@ -2157,7 +2157,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>4</v>
@@ -2171,7 +2171,7 @@
         <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>4</v>

--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/backend.devsiruhay/modules/training/database/masters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEEE3C2-3858-9644-A9DA-D48B8B172897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1229CB-DB68-A044-A6BE-C34809642424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28320" windowHeight="21600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="86">
   <si>
     <t>module</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>blue-grey</t>
-  </si>
-  <si>
-    <t>backend</t>
   </si>
   <si>
     <t>school</t>
@@ -713,13 +710,13 @@
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>34</v>
@@ -727,11 +724,9 @@
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H2" s="5" t="b">
         <v>1</v>
@@ -743,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -807,7 +802,7 @@
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>21</v>
@@ -816,13 +811,13 @@
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>23</v>
@@ -839,25 +834,25 @@
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H3" s="5" t="b">
         <v>1</v>
@@ -871,25 +866,25 @@
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="H4" s="5" t="b">
         <v>0</v>
@@ -903,25 +898,25 @@
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="H5" s="5" t="b">
         <v>0</v>
@@ -935,25 +930,25 @@
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="H6" s="5" t="b">
         <v>0</v>
@@ -967,25 +962,25 @@
     </row>
     <row r="7" spans="1:11" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="H7" s="5" t="b">
         <v>0</v>
@@ -999,25 +994,25 @@
     </row>
     <row r="8" spans="1:11" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="H8" s="5" t="b">
         <v>0</v>
@@ -1031,25 +1026,25 @@
     </row>
     <row r="9" spans="1:11" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="H9" s="5" t="b">
         <v>0</v>
@@ -1063,25 +1058,25 @@
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H10" s="5" t="b">
         <v>1</v>
@@ -1095,25 +1090,25 @@
     </row>
     <row r="11" spans="1:11" ht="18" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H11" s="5" t="b">
         <v>0</v>
@@ -1127,25 +1122,25 @@
     </row>
     <row r="12" spans="1:11" ht="18" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H12" s="5" t="b">
         <v>0</v>
@@ -1159,25 +1154,25 @@
     </row>
     <row r="13" spans="1:11" ht="18" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H13" s="5" t="b">
         <v>0</v>
@@ -1191,25 +1186,25 @@
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" s="5" t="b">
         <v>0</v>
@@ -1223,25 +1218,25 @@
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15" s="5" t="b">
         <v>0</v>
@@ -1255,25 +1250,25 @@
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16" s="5" t="b">
         <v>0</v>
@@ -1287,7 +1282,7 @@
     </row>
     <row r="17" spans="1:11" ht="18" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
@@ -1296,13 +1291,13 @@
         <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>27</v>
@@ -1319,25 +1314,25 @@
     </row>
     <row r="18" spans="1:11" ht="18" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="H18" s="5" t="b">
         <v>0</v>
@@ -1351,25 +1346,25 @@
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="H19" s="5" t="b">
         <v>0</v>
@@ -1412,10 +1407,10 @@
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
@@ -1423,10 +1418,10 @@
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
@@ -1434,10 +1429,10 @@
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -1445,10 +1440,10 @@
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
@@ -1456,10 +1451,10 @@
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
@@ -1467,10 +1462,10 @@
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
@@ -1478,10 +1473,10 @@
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
@@ -1489,10 +1484,10 @@
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
@@ -1500,10 +1495,10 @@
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
@@ -1511,76 +1506,76 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
@@ -1588,10 +1583,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
@@ -1599,10 +1594,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
@@ -1635,7 +1630,7 @@
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
@@ -1643,7 +1638,7 @@
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -1651,18 +1646,18 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1696,200 +1691,200 @@
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1927,13 +1922,13 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
@@ -1941,13 +1936,13 @@
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
@@ -1955,13 +1950,13 @@
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
@@ -1969,13 +1964,13 @@
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -1983,13 +1978,13 @@
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
@@ -1997,13 +1992,13 @@
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -2011,13 +2006,13 @@
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
@@ -2025,13 +2020,13 @@
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>4</v>
@@ -2039,13 +2034,13 @@
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>
@@ -2053,13 +2048,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>4</v>
@@ -2067,13 +2062,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
@@ -2081,13 +2076,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
@@ -2095,13 +2090,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -2109,13 +2104,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -2123,13 +2118,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
@@ -2137,13 +2132,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>4</v>
@@ -2151,13 +2146,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>4</v>
@@ -2165,13 +2160,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>4</v>

--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1229CB-DB68-A044-A6BE-C34809642424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC48F8C2-D4B1-9941-BF46-6330432C8003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="91">
   <si>
     <t>module</t>
   </si>
@@ -276,20 +276,35 @@
     <t>view, show, search</t>
   </si>
   <si>
-    <t>committee-chairman</t>
-  </si>
-  <si>
-    <t>committee-member</t>
-  </si>
-  <si>
-    <t>superadmin, administrator, committee-chairman, committee-member</t>
+    <t>Pengaturan</t>
+  </si>
+  <si>
+    <t>training-setting</t>
+  </si>
+  <si>
+    <t>setting</t>
+  </si>
+  <si>
+    <t>moderator</t>
+  </si>
+  <si>
+    <t>fellow</t>
+  </si>
+  <si>
+    <t>superadmin, administrator</t>
+  </si>
+  <si>
+    <t>superadmin, administrator, moderator, fellow</t>
+  </si>
+  <si>
+    <t>settings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +324,22 @@
       <color rgb="FF000000"/>
       <name val="Fira Code Regular"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Fira Code"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Fira Code"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Fira Code"/>
     </font>
   </fonts>
   <fills count="2">
@@ -338,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -357,6 +388,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,7 +791,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -1376,6 +1416,38 @@
         <v>24</v>
       </c>
     </row>
+    <row r="20" spans="1:11" ht="18" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1386,7 +1458,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -1600,6 +1672,17 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1621,43 +1704,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>83</v>
+      <c r="A4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>84</v>
+      <c r="A5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1753,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -1678,7 +1761,7 @@
     <col min="3" max="3" width="65.83203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" customHeight="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1689,7 +1772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18" customHeight="1">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
@@ -1697,10 +1780,10 @@
         <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -1708,10 +1791,10 @@
         <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1719,10 +1802,10 @@
         <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -1730,10 +1813,10 @@
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1741,10 +1824,10 @@
         <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1752,10 +1835,10 @@
         <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -1763,10 +1846,10 @@
         <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1774,10 +1857,10 @@
         <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -1785,7 +1868,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1796,7 +1879,7 @@
         <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1807,7 +1890,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1818,7 +1901,7 @@
         <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1829,7 +1912,7 @@
         <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1840,7 +1923,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1851,7 +1934,7 @@
         <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1862,7 +1945,7 @@
         <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1873,7 +1956,7 @@
         <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1884,7 +1967,18 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1897,7 +1991,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -1906,7 +2000,7 @@
     <col min="4" max="4" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1920,7 +2014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>37</v>
       </c>
@@ -1928,13 +2022,13 @@
         <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -1942,13 +2036,13 @@
         <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="18" customHeight="1">
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>37</v>
       </c>
@@ -1956,13 +2050,13 @@
         <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -1970,13 +2064,13 @@
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1">
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -1984,13 +2078,13 @@
         <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>37</v>
       </c>
@@ -1998,13 +2092,13 @@
         <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1">
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -2012,13 +2106,13 @@
         <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" customHeight="1">
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -2026,13 +2120,13 @@
         <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" customHeight="1">
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -2040,7 +2134,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>
@@ -2054,7 +2148,7 @@
         <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>4</v>
@@ -2068,7 +2162,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
@@ -2082,7 +2176,7 @@
         <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
@@ -2096,7 +2190,7 @@
         <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -2110,7 +2204,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -2124,7 +2218,7 @@
         <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
@@ -2138,7 +2232,7 @@
         <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>4</v>
@@ -2152,7 +2246,7 @@
         <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>4</v>
@@ -2166,9 +2260,23 @@
         <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>4</v>
       </c>
     </row>

--- a/database/masters/base-seeder.xlsx
+++ b/database/masters/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Herd/devsiruhay/modules/training/database/masters/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC48F8C2-D4B1-9941-BF46-6330432C8003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBA5433-1173-C840-AAC8-A11E8A54AD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>module</t>
   </si>
@@ -294,10 +294,13 @@
     <t>superadmin, administrator</t>
   </si>
   <si>
-    <t>superadmin, administrator, moderator, fellow</t>
-  </si>
-  <si>
     <t>settings</t>
+  </si>
+  <si>
+    <t>officer</t>
+  </si>
+  <si>
+    <t>superadmin, administrator, officer, moderator, fellow</t>
   </si>
 </sst>
 </file>
@@ -369,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -398,6 +401,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1430,7 +1434,7 @@
         <v>84</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>37</v>
@@ -1696,14 +1700,15 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1711,7 +1716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1">
+    <row r="2" spans="1:2">
       <c r="A2" s="8" t="s">
         <v>37</v>
       </c>
@@ -1719,7 +1724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1">
+    <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
         <v>37</v>
       </c>
@@ -1741,6 +1746,14 @@
       </c>
       <c r="B5" s="9" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1780,7 +1793,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1791,7 +1804,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1802,7 +1815,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1813,7 +1826,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1824,7 +1837,7 @@
         <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1835,7 +1848,7 @@
         <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1846,7 +1859,7 @@
         <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1857,7 +1870,7 @@
         <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1868,7 +1881,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1879,7 +1892,7 @@
         <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1890,7 +1903,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1901,7 +1914,7 @@
         <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1912,7 +1925,7 @@
         <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1923,7 +1936,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1934,7 +1947,7 @@
         <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1945,7 +1958,7 @@
         <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2022,7 +2035,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
@@ -2036,7 +2049,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>4</v>
@@ -2050,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>4</v>
@@ -2064,7 +2077,7 @@
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -2078,7 +2091,7 @@
         <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>4</v>
@@ -2092,7 +2105,7 @@
         <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -2106,7 +2119,7 @@
         <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>4</v>
@@ -2120,7 +2133,7 @@
         <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>4</v>
@@ -2134,7 +2147,7 @@
         <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>4</v>
@@ -2148,7 +2161,7 @@
         <v>76</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>4</v>
@@ -2162,7 +2175,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>4</v>
@@ -2176,7 +2189,7 @@
         <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>4</v>
@@ -2190,7 +2203,7 @@
         <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -2204,7 +2217,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>4</v>
@@ -2218,7 +2231,7 @@
         <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>4</v>
@@ -2232,7 +2245,7 @@
         <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>4</v>
